--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488080_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488080_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5414</v>
+        <v>5.9022</v>
       </c>
       <c r="E2" t="n">
-        <v>8.515599999999999</v>
+        <v>8.6799</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.9742</v>
+        <v>-2.7777</v>
       </c>
       <c r="G2" t="n">
         <v>2.9102</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1721</v>
+        <v>-0.8113</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2641</v>
+        <v>-0.0998</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.908</v>
+        <v>-0.7114</v>
       </c>
       <c r="V2" t="n">
         <v>4.1997</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ ASTILLEROS</t>
+          <t>A. BUALÓ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1013</v>
+        <v>1.508</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4178</v>
+        <v>1.508</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3165</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1556</v>
+        <v>1.508</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0674</v>
+        <v>0.3027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0881</v>
+        <v>1.2053</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9127999999999999</v>
+        <v>1.508</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4514</v>
+        <v>0.3027</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4614</v>
+        <v>1.2053</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7572</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3839</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3733</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9462</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.531</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4153</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9817</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.9474</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BUALÓ</t>
+          <t>A. MARTINEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.508</v>
+        <v>1.3934</v>
       </c>
       <c r="E4" t="n">
-        <v>1.508</v>
+        <v>0.7163</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.6771</v>
       </c>
       <c r="G4" t="n">
-        <v>1.508</v>
+        <v>0.8329</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3027</v>
+        <v>0.1289</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2053</v>
+        <v>0.704</v>
       </c>
       <c r="J4" t="n">
-        <v>1.508</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3027</v>
+        <v>0.1211</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2053</v>
+        <v>0.6869</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.0171</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.3029</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.0917</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.2112</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MARTINEZ GONZALEZ</t>
+          <t>A. VAZQUEZ ASTILLEROS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9297</v>
+        <v>0.8433</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3088</v>
+        <v>1.6652</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6209</v>
+        <v>-0.8219</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8329</v>
+        <v>0.1556</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1289</v>
+        <v>0.0674</v>
       </c>
       <c r="I5" t="n">
-        <v>0.704</v>
+        <v>0.0881</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1211</v>
+        <v>0.4514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6869</v>
+        <v>0.4614</v>
       </c>
       <c r="M5" t="n">
-        <v>0.025</v>
+        <v>-0.7572</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0078</v>
+        <v>-0.3839</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0171</v>
+        <v>-0.3733</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7929</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7665</v>
+        <v>0.6883</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4992</v>
+        <v>0.7784</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2673</v>
+        <v>-0.0901</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0704</v>
+        <v>1.9817</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.9474</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0704</v>
+        <v>-0.9657</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5941</v>
+        <v>0.2708</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9375</v>
+        <v>0.5301</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3435</v>
+        <v>-0.2592</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2147</v>
@@ -922,13 +922,13 @@
         <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6105</v>
+        <v>0.2873</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5543</v>
+        <v>0.1469</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0562</v>
+        <v>0.1404</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0692</v>
+        <v>0.1535</v>
       </c>
       <c r="E7" t="n">
         <v>1.2216</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1524</v>
+        <v>-1.0681</v>
       </c>
       <c r="G7" t="n">
         <v>0.9485</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0562</v>
+        <v>0.1404</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2222</v>
+        <v>-0.9518</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.471</v>
+        <v>-1.3692</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2489</v>
+        <v>0.4174</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1473</v>
@@ -1078,13 +1078,13 @@
         <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6695</v>
+        <v>-0.3992</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3744</v>
+        <v>-0.2725</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2952</v>
+        <v>-0.1267</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ CAMPOS</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8315</v>
+        <v>-2.067</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.4155</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8632</v>
+        <v>-1.6515</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4216</v>
+        <v>-1.373</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7958</v>
+        <v>0.7909</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6257</v>
+        <v>-2.1639</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4529</v>
+        <v>0.8804</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6137</v>
+        <v>1.3185</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1607</v>
+        <v>-0.4381</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9686</v>
+        <v>-2.2534</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1822</v>
+        <v>-0.5276</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7864</v>
+        <v>-1.7258</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7929</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1593</v>
+        <v>-0.1588</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4847</v>
+        <v>0.0322</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3254</v>
+        <v>-0.191</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3621</v>
+        <v>-0.337</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>H. FERNANDEZ CAMPOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1689</v>
+        <v>-2.2285</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5173</v>
+        <v>-1.4776</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6515</v>
+        <v>-0.7509</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.373</v>
+        <v>-2.4216</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7909</v>
+        <v>-1.7958</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1639</v>
+        <v>-0.6257</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8804</v>
+        <v>-1.4529</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3185</v>
+        <v>-1.6137</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4381</v>
+        <v>0.1607</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2534</v>
+        <v>-0.9686</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5276</v>
+        <v>-0.1822</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7258</v>
+        <v>-0.7864</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2606</v>
+        <v>-0.2377</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0696</v>
+        <v>-0.0246</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.191</v>
+        <v>-0.213</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.337</v>
+        <v>-0.3621</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3621</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7141</v>
+        <v>-2.9314</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4584</v>
+        <v>1.4377</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.1725</v>
+        <v>-4.369</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0684</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6472</v>
+        <v>-0.8645</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6223</v>
+        <v>-0.6431</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0249</v>
+        <v>-0.2214</v>
       </c>
       <c r="V11" t="n">
         <v>1.7855</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>B. HUNT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5239</v>
+        <v>-4.4059</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.886</v>
+        <v>-1.9824</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6379</v>
+        <v>-2.4235</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4893</v>
+        <v>-4.0018</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.036</v>
+        <v>-2.9017</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4534</v>
+        <v>-1.1001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3261</v>
+        <v>-1.8282</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5782</v>
+        <v>-1.9163</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7478</v>
+        <v>0.0881</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1633</v>
+        <v>-2.1736</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4577</v>
+        <v>-0.9853</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2945</v>
+        <v>-1.1882</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.276</v>
+        <v>-0.8094</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4223</v>
+        <v>-0.6367</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6983</v>
+        <v>-0.1727</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5692</v>
+        <v>0.6036</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5692</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. HUNT</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8548</v>
+        <v>-4.6049</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.656</v>
+        <v>-3.1916</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1989</v>
+        <v>-1.4133</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.0018</v>
+        <v>-1.4893</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.9017</v>
+        <v>-1.036</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1001</v>
+        <v>-0.4534</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8282</v>
+        <v>-1.3261</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.9163</v>
+        <v>-0.5782</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0881</v>
+        <v>-0.7478</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1736</v>
+        <v>-0.1633</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9853</v>
+        <v>-0.4577</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1882</v>
+        <v>0.2945</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R13" t="n">
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2584</v>
+        <v>-0.357</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3103</v>
+        <v>0.1167</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0519</v>
+        <v>-0.4737</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6036</v>
+        <v>-1.5692</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8701</v>
+        <v>-1.5692</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.6017</v>
+        <v>-5.743</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9111</v>
+        <v>-1.0524</v>
       </c>
       <c r="F14" t="n">
         <v>-4.6906</v>
@@ -1546,10 +1546,10 @@
         <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9287</v>
+        <v>-1.0701</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5064</v>
+        <v>-0.6478</v>
       </c>
       <c r="U14" t="n">
         <v>-0.4223</v>
@@ -1579,31 +1579,31 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.1734</v>
+        <v>-12.8613</v>
       </c>
       <c r="E15" t="n">
-        <v>5.958099999999997</v>
+        <v>6.270099999999998</v>
       </c>
       <c r="F15" t="n">
-        <v>-19.1314</v>
+        <v>-19.1312</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.051600000000001</v>
+        <v>-9.051599999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.646899999999999</v>
+        <v>-3.6469</v>
       </c>
       <c r="I15" t="n">
         <v>-5.404600000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>8.329599999999999</v>
+        <v>8.329599999999997</v>
       </c>
       <c r="K15" t="n">
         <v>2.5596</v>
       </c>
       <c r="L15" t="n">
-        <v>5.770099999999999</v>
+        <v>5.7701</v>
       </c>
       <c r="M15" t="n">
         <v>-17.3811</v>
@@ -1615,7 +1615,7 @@
         <v>-11.1746</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.9554</v>
+        <v>-4.955399999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>-14.8665</v>
@@ -1624,28 +1624,28 @@
         <v>9.911099999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.3316</v>
+        <v>-4.0197</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7788</v>
+        <v>-1.4668</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.5528</v>
+        <v>-2.5527</v>
       </c>
       <c r="V15" t="n">
-        <v>5.165500000000002</v>
+        <v>5.1655</v>
       </c>
       <c r="W15" t="n">
         <v>14.2741</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.108599999999999</v>
+        <v>-9.108600000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9253</v>
+        <v>7.4642</v>
       </c>
       <c r="E16" t="n">
-        <v>5.195</v>
+        <v>8.764699999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7303</v>
+        <v>-1.3005</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5686</v>
+        <v>6.0973</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0178</v>
+        <v>1.6817</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5508</v>
+        <v>4.4157</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0538</v>
+        <v>7.5301</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6035</v>
+        <v>1.9376</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4503</v>
+        <v>5.5925</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4852</v>
+        <v>-1.4328</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5857</v>
+        <v>-0.256</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8995</v>
+        <v>-1.1768</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2357</v>
+        <v>0.5672</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0658</v>
+        <v>0.0029</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3016</v>
+        <v>0.5642</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9405</v>
+        <v>0.7997</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2071</v>
+        <v>3.2139</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2666</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.7022</v>
+        <v>7.2377</v>
       </c>
       <c r="E17" t="n">
-        <v>8.2554</v>
+        <v>5.6025</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5532</v>
+        <v>1.6352</v>
       </c>
       <c r="G17" t="n">
-        <v>6.0973</v>
+        <v>2.5686</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6817</v>
+        <v>2.0178</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4157</v>
+        <v>0.5508</v>
       </c>
       <c r="J17" t="n">
-        <v>7.5301</v>
+        <v>4.0538</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9376</v>
+        <v>2.6035</v>
       </c>
       <c r="L17" t="n">
-        <v>5.5925</v>
+        <v>1.4503</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4328</v>
+        <v>-1.4852</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.256</v>
+        <v>-0.5857</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1768</v>
+        <v>-0.8995</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1949</v>
+        <v>1.5481</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5064</v>
+        <v>0.3416</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3115</v>
+        <v>1.2065</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7997</v>
+        <v>0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2139</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4142</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2955</v>
+        <v>2.4183</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1213</v>
+        <v>2.0194</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1742</v>
+        <v>0.3988</v>
       </c>
       <c r="G18" t="n">
         <v>0.4357</v>
@@ -1858,13 +1858,13 @@
         <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2563</v>
+        <v>0.379</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2975</v>
+        <v>0.1956</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0412</v>
+        <v>0.1834</v>
       </c>
       <c r="V18" t="n">
         <v>1.2071</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0576</v>
+        <v>1.8726</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2172</v>
+        <v>0.5978</v>
       </c>
       <c r="F19" t="n">
         <v>1.2748</v>
@@ -1936,10 +1936,10 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0352</v>
+        <v>-0.2203</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6753</v>
+        <v>0.1396</v>
       </c>
       <c r="U19" t="n">
         <v>-0.3599</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7689</v>
+        <v>0.724</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9608</v>
+        <v>3.6288</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1919</v>
+        <v>-2.9048</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2604</v>
+        <v>1.17</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4454</v>
+        <v>1.5985</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8149999999999999</v>
+        <v>-0.4285</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0393</v>
+        <v>2.6705</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2358</v>
+        <v>2.0523</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8036</v>
+        <v>0.6182</v>
       </c>
       <c r="M20" t="n">
-        <v>0.221</v>
+        <v>-1.5005</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2096</v>
+        <v>-0.4538</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0114</v>
+        <v>-1.0467</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4559</v>
+        <v>0.77</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9215</v>
+        <v>0.337</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4655</v>
+        <v>0.433</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7403</v>
+        <v>-1.8107</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7403</v>
+        <v>-3.6213</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7667</v>
+        <v>0.112</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1364</v>
+        <v>1.2477</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6304</v>
+        <v>-1.1357</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0455</v>
+        <v>1.2604</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.06</v>
+        <v>0.4454</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9855</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6883</v>
+        <v>1.0393</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0097</v>
+        <v>0.2358</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3214</v>
+        <v>0.8036</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3572</v>
+        <v>0.221</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0503</v>
+        <v>0.2096</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3069</v>
+        <v>0.0114</v>
       </c>
       <c r="P21" t="n">
         <v>0.7929</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>3.0194</v>
+        <v>-0.201</v>
       </c>
       <c r="T21" t="n">
-        <v>3.014</v>
+        <v>0.2084</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0053</v>
+        <v>-0.4094</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6222</v>
+        <v>-1.1303</v>
       </c>
       <c r="E22" t="n">
-        <v>3.527</v>
+        <v>-1.901</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9048</v>
+        <v>0.7708</v>
       </c>
       <c r="G22" t="n">
-        <v>1.17</v>
+        <v>-3.0455</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5985</v>
+        <v>-2.06</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4285</v>
+        <v>-0.9855</v>
       </c>
       <c r="J22" t="n">
-        <v>2.6705</v>
+        <v>-1.6883</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0523</v>
+        <v>-2.0097</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6182</v>
+        <v>0.3214</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5005</v>
+        <v>-1.3572</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4538</v>
+        <v>-0.0503</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0467</v>
+        <v>-1.3069</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R22" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6681</v>
+        <v>1.1224</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2351</v>
+        <v>0.9766</v>
       </c>
       <c r="U22" t="n">
-        <v>0.433</v>
+        <v>0.1457</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.6213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERRERA</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4091</v>
+        <v>-1.2517</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2003</v>
+        <v>-0.768</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2089</v>
+        <v>-0.4837</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1485</v>
+        <v>-1.1839</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7869</v>
+        <v>0.5704</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3616</v>
+        <v>-1.7543</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0604</v>
+        <v>-1.5561</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0202</v>
+        <v>0.3568</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0402</v>
+        <v>-1.913</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2089</v>
+        <v>0.3722</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8071</v>
+        <v>0.2136</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4018</v>
+        <v>0.1586</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0624</v>
+        <v>0.2166</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0624</v>
+        <v>0.1846</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5854</v>
+        <v>-1.3181</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0736</v>
+        <v>0.4582</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5118</v>
+        <v>-1.7763</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1839</v>
+        <v>0.1496</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5704</v>
+        <v>0.4021</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7543</v>
+        <v>-0.2525</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5561</v>
+        <v>1.6034</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3568</v>
+        <v>1.0694</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.913</v>
+        <v>0.534</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3722</v>
+        <v>-1.4538</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2136</v>
+        <v>-0.6674</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1586</v>
+        <v>-0.7864</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1893</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1171</v>
+        <v>0.1358</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.121</v>
+        <v>0.0441</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0039</v>
+        <v>0.0917</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4737</v>
+        <v>-1.2071</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.0772</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>J. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8379</v>
+        <v>-1.4091</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0507</v>
+        <v>-0.2003</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8886</v>
+        <v>-1.2089</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1496</v>
+        <v>-1.1485</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4021</v>
+        <v>-0.7869</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2525</v>
+        <v>-0.3616</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6034</v>
+        <v>0.0604</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0694</v>
+        <v>0.0202</v>
       </c>
       <c r="L25" t="n">
-        <v>0.534</v>
+        <v>0.0402</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4538</v>
+        <v>-1.2089</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6674</v>
+        <v>-0.8071</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7864</v>
+        <v>-0.4018</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.384</v>
+        <v>-0.0624</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3634</v>
+        <v>-0.0624</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0206</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.1327</v>
+        <v>-1.5463</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6242</v>
+        <v>-0.3186</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5085</v>
+        <v>-1.2277</v>
       </c>
       <c r="G26" t="n">
         <v>-0.131</v>
@@ -2482,13 +2482,13 @@
         <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5102</v>
+        <v>0.0762</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.121</v>
+        <v>0.1846</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3892</v>
+        <v>-0.1084</v>
       </c>
       <c r="V26" t="n">
         <v>-2.6808</v>
@@ -2518,16 +2518,16 @@
         <v>13.1733</v>
       </c>
       <c r="E27" t="n">
-        <v>19.1313</v>
+        <v>19.1312</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.957999999999999</v>
+        <v>-5.958</v>
       </c>
       <c r="G27" t="n">
         <v>9.051599999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>3.6471</v>
+        <v>3.647099999999999</v>
       </c>
       <c r="I27" t="n">
         <v>5.404599999999999</v>
@@ -2536,7 +2536,7 @@
         <v>17.3811</v>
       </c>
       <c r="K27" t="n">
-        <v>6.206499999999999</v>
+        <v>6.2065</v>
       </c>
       <c r="L27" t="n">
         <v>11.1747</v>
@@ -2548,7 +2548,7 @@
         <v>-2.5596</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.77</v>
+        <v>-5.769999999999999</v>
       </c>
       <c r="P27" t="n">
         <v>4.9556</v>
@@ -2563,16 +2563,16 @@
         <v>4.3316</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5528</v>
+        <v>2.5526</v>
       </c>
       <c r="U27" t="n">
-        <v>1.7789</v>
+        <v>1.7788</v>
       </c>
       <c r="V27" t="n">
         <v>-5.1656</v>
       </c>
       <c r="W27" t="n">
-        <v>9.108700000000001</v>
+        <v>9.108699999999999</v>
       </c>
       <c r="X27" t="n">
         <v>-14.2741</v>
